--- a/bra_urls.xlsx
+++ b/bra_urls.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="485">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="761" uniqueCount="761">
   <si>
     <t>x</t>
   </si>
@@ -743,40 +743,460 @@
     <t>242</t>
   </si>
   <si>
+    <t>243</t>
+  </si>
+  <si>
+    <t>244</t>
+  </si>
+  <si>
+    <t>245</t>
+  </si>
+  <si>
+    <t>246</t>
+  </si>
+  <si>
+    <t>247</t>
+  </si>
+  <si>
+    <t>248</t>
+  </si>
+  <si>
+    <t>249</t>
+  </si>
+  <si>
+    <t>250</t>
+  </si>
+  <si>
+    <t>251</t>
+  </si>
+  <si>
+    <t>252</t>
+  </si>
+  <si>
+    <t>253</t>
+  </si>
+  <si>
+    <t>254</t>
+  </si>
+  <si>
+    <t>255</t>
+  </si>
+  <si>
+    <t>256</t>
+  </si>
+  <si>
+    <t>257</t>
+  </si>
+  <si>
+    <t>258</t>
+  </si>
+  <si>
+    <t>259</t>
+  </si>
+  <si>
+    <t>260</t>
+  </si>
+  <si>
+    <t>261</t>
+  </si>
+  <si>
+    <t>262</t>
+  </si>
+  <si>
+    <t>263</t>
+  </si>
+  <si>
+    <t>264</t>
+  </si>
+  <si>
+    <t>265</t>
+  </si>
+  <si>
+    <t>266</t>
+  </si>
+  <si>
+    <t>267</t>
+  </si>
+  <si>
+    <t>268</t>
+  </si>
+  <si>
+    <t>269</t>
+  </si>
+  <si>
+    <t>270</t>
+  </si>
+  <si>
+    <t>271</t>
+  </si>
+  <si>
+    <t>272</t>
+  </si>
+  <si>
+    <t>273</t>
+  </si>
+  <si>
+    <t>274</t>
+  </si>
+  <si>
+    <t>275</t>
+  </si>
+  <si>
+    <t>276</t>
+  </si>
+  <si>
+    <t>277</t>
+  </si>
+  <si>
+    <t>278</t>
+  </si>
+  <si>
+    <t>279</t>
+  </si>
+  <si>
+    <t>280</t>
+  </si>
+  <si>
+    <t>281</t>
+  </si>
+  <si>
+    <t>282</t>
+  </si>
+  <si>
+    <t>283</t>
+  </si>
+  <si>
+    <t>284</t>
+  </si>
+  <si>
+    <t>285</t>
+  </si>
+  <si>
+    <t>286</t>
+  </si>
+  <si>
+    <t>287</t>
+  </si>
+  <si>
+    <t>288</t>
+  </si>
+  <si>
+    <t>289</t>
+  </si>
+  <si>
+    <t>290</t>
+  </si>
+  <si>
+    <t>291</t>
+  </si>
+  <si>
+    <t>292</t>
+  </si>
+  <si>
+    <t>293</t>
+  </si>
+  <si>
+    <t>294</t>
+  </si>
+  <si>
+    <t>295</t>
+  </si>
+  <si>
+    <t>296</t>
+  </si>
+  <si>
+    <t>297</t>
+  </si>
+  <si>
+    <t>298</t>
+  </si>
+  <si>
+    <t>299</t>
+  </si>
+  <si>
+    <t>300</t>
+  </si>
+  <si>
+    <t>301</t>
+  </si>
+  <si>
+    <t>302</t>
+  </si>
+  <si>
+    <t>303</t>
+  </si>
+  <si>
+    <t>304</t>
+  </si>
+  <si>
+    <t>305</t>
+  </si>
+  <si>
+    <t>306</t>
+  </si>
+  <si>
+    <t>307</t>
+  </si>
+  <si>
+    <t>308</t>
+  </si>
+  <si>
+    <t>309</t>
+  </si>
+  <si>
+    <t>310</t>
+  </si>
+  <si>
+    <t>311</t>
+  </si>
+  <si>
+    <t>312</t>
+  </si>
+  <si>
+    <t>313</t>
+  </si>
+  <si>
+    <t>314</t>
+  </si>
+  <si>
+    <t>315</t>
+  </si>
+  <si>
+    <t>316</t>
+  </si>
+  <si>
+    <t>317</t>
+  </si>
+  <si>
+    <t>318</t>
+  </si>
+  <si>
+    <t>319</t>
+  </si>
+  <si>
+    <t>320</t>
+  </si>
+  <si>
+    <t>321</t>
+  </si>
+  <si>
+    <t>322</t>
+  </si>
+  <si>
+    <t>323</t>
+  </si>
+  <si>
+    <t>324</t>
+  </si>
+  <si>
+    <t>325</t>
+  </si>
+  <si>
+    <t>326</t>
+  </si>
+  <si>
+    <t>327</t>
+  </si>
+  <si>
+    <t>328</t>
+  </si>
+  <si>
+    <t>329</t>
+  </si>
+  <si>
+    <t>330</t>
+  </si>
+  <si>
+    <t>331</t>
+  </si>
+  <si>
+    <t>332</t>
+  </si>
+  <si>
+    <t>333</t>
+  </si>
+  <si>
+    <t>334</t>
+  </si>
+  <si>
+    <t>335</t>
+  </si>
+  <si>
+    <t>336</t>
+  </si>
+  <si>
+    <t>337</t>
+  </si>
+  <si>
+    <t>338</t>
+  </si>
+  <si>
+    <t>339</t>
+  </si>
+  <si>
+    <t>340</t>
+  </si>
+  <si>
+    <t>341</t>
+  </si>
+  <si>
+    <t>342</t>
+  </si>
+  <si>
+    <t>343</t>
+  </si>
+  <si>
+    <t>344</t>
+  </si>
+  <si>
+    <t>345</t>
+  </si>
+  <si>
+    <t>346</t>
+  </si>
+  <si>
+    <t>347</t>
+  </si>
+  <si>
+    <t>348</t>
+  </si>
+  <si>
+    <t>349</t>
+  </si>
+  <si>
+    <t>350</t>
+  </si>
+  <si>
+    <t>351</t>
+  </si>
+  <si>
+    <t>352</t>
+  </si>
+  <si>
+    <t>353</t>
+  </si>
+  <si>
+    <t>354</t>
+  </si>
+  <si>
+    <t>355</t>
+  </si>
+  <si>
+    <t>356</t>
+  </si>
+  <si>
+    <t>357</t>
+  </si>
+  <si>
+    <t>358</t>
+  </si>
+  <si>
+    <t>359</t>
+  </si>
+  <si>
+    <t>360</t>
+  </si>
+  <si>
+    <t>361</t>
+  </si>
+  <si>
+    <t>362</t>
+  </si>
+  <si>
+    <t>363</t>
+  </si>
+  <si>
+    <t>364</t>
+  </si>
+  <si>
+    <t>365</t>
+  </si>
+  <si>
+    <t>366</t>
+  </si>
+  <si>
+    <t>367</t>
+  </si>
+  <si>
+    <t>368</t>
+  </si>
+  <si>
+    <t>369</t>
+  </si>
+  <si>
+    <t>370</t>
+  </si>
+  <si>
+    <t>371</t>
+  </si>
+  <si>
+    <t>372</t>
+  </si>
+  <si>
+    <t>373</t>
+  </si>
+  <si>
+    <t>374</t>
+  </si>
+  <si>
+    <t>375</t>
+  </si>
+  <si>
+    <t>376</t>
+  </si>
+  <si>
+    <t>377</t>
+  </si>
+  <si>
+    <t>378</t>
+  </si>
+  <si>
+    <t>379</t>
+  </si>
+  <si>
+    <t>380</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/620b512a/Internacional-Bahia-April-13-2024-Serie-A</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/60ef737d/Criciuma-Juventude-April-13-2024-Serie-A</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/620b512a/Internacional-Bahia-April-13-2024-Serie-A</t>
+    <t>https://fbref.com/en/matches/865e8350/Vasco-da-Gama-Gremio-April-14-2024-Serie-A</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/086cf01e/Athletico-Paranaense-Cuiaba-April-14-2024-Serie-A</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/865e8350/Vasco-da-Gama-Gremio-April-14-2024-Serie-A</t>
+    <t>https://fbref.com/en/matches/d95fadf2/Atletico-Goianiense-Flamengo-April-14-2024-Serie-A</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/d3926429/Corinthians-Atletico-Mineiro-April-14-2024-Serie-A</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/d95fadf2/Atletico-Goianiense-Flamengo-April-14-2024-Serie-A</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/37353de0/Cruzeiro-Botafogo-RJ-April-14-2024-Serie-A</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/e8d2edb8/Vitoria-Palmeiras-April-14-2024-Serie-A</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/93f72e31/Sao-Paulo-Fortaleza-April-13-2024-Serie-A</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/5aee04aa/Fluminense-Red-Bull-Bragantino-April-13-2024-Serie-A</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/93f72e31/Sao-Paulo-Fortaleza-April-13-2024-Serie-A</t>
+    <t>https://fbref.com/en/matches/4ad46089/Red-Bull-Bragantino-Vasco-da-Gama-April-17-2024-Serie-A</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/12462f89/Gremio-Athletico-Paranaense-April-17-2024-Serie-A</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/4ad46089/Red-Bull-Bragantino-Vasco-da-Gama-April-17-2024-Serie-A</t>
+    <t>https://fbref.com/en/matches/5447208f/Palmeiras-Internacional-April-17-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/69ea969f/Fortaleza-Cruzeiro-April-17-2024-Serie-A</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/11eccb6a/Juventude-Corinthians-April-17-2024-Serie-A</t>
@@ -785,12 +1205,6 @@
     <t>https://fbref.com/en/matches/1d4e7bb0/Atletico-Mineiro-Criciuma-April-17-2024-Serie-A</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/5447208f/Palmeiras-Internacional-April-17-2024-Serie-A</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/69ea969f/Fortaleza-Cruzeiro-April-17-2024-Serie-A</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/c7829e3b/Bahia-Fluminense-April-16-2024-Serie-A</t>
   </si>
   <si>
@@ -812,12 +1226,12 @@
     <t>https://fbref.com/en/matches/0d52ac06/Vitoria-Bahia-April-21-2024-Serie-A</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/eccd538c/Athletico-Paranaense-Internacional-April-21-2024-Serie-A</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/a47977b4/Palmeiras-Flamengo-April-21-2024-Serie-A</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/eccd538c/Athletico-Paranaense-Internacional-April-21-2024-Serie-A</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/90efe95f/Atletico-Goianiense-Sao-Paulo-April-21-2024-Serie-A</t>
   </si>
   <si>
@@ -836,12 +1250,12 @@
     <t>https://fbref.com/en/matches/c6c5b0eb/Flamengo-Botafogo-RJ-April-28-2024-Serie-A</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/a8cf2dc2/Corinthians-Fluminense-April-28-2024-Serie-A</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/2ec6867f/Cruzeiro-Vitoria-April-28-2024-Serie-A</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/a8cf2dc2/Corinthians-Fluminense-April-28-2024-Serie-A</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/4bfd8bae/Fortaleza-Red-Bull-Bragantino-April-28-2024-Serie-A</t>
   </si>
   <si>
@@ -881,21 +1295,21 @@
     <t>https://fbref.com/en/matches/206a47aa/Flamengo-Corinthians-May-11-2024-Serie-A</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/fec27399/Fortaleza-Botafogo-RJ-May-12-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/c7b55047/Atletico-Goianiense-Cruzeiro-May-12-2024-Serie-A</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/73bffc53/Palmeiras-Athletico-Paranaense-May-12-2024-Serie-A</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/c7b55047/Atletico-Goianiense-Cruzeiro-May-12-2024-Serie-A</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/fec27399/Fortaleza-Botafogo-RJ-May-12-2024-Serie-A</t>
+    <t>https://fbref.com/en/matches/cbb799c7/Vasco-da-Gama-Vitoria-May-12-2024-Serie-A</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/b6e02908/Bahia-Red-Bull-Bragantino-May-12-2024-Serie-A</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/cbb799c7/Vasco-da-Gama-Vitoria-May-12-2024-Serie-A</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/7a7905d4/Sao-Paulo-Fluminense-May-13-2024-Serie-A</t>
   </si>
   <si>
@@ -953,45 +1367,45 @@
     <t>https://fbref.com/en/matches/35b9c8c7/Cruzeiro-Cuiaba-June-13-2024-Serie-A</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/a847c862/Internacional-Sao-Paulo-June-13-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/e3954d94/Athletico-Paranaense-Criciuma-June-13-2024-Serie-A</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/98b435e7/Flamengo-Gremio-June-13-2024-Serie-A</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/a847c862/Internacional-Sao-Paulo-June-13-2024-Serie-A</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/e3954d94/Athletico-Paranaense-Criciuma-June-13-2024-Serie-A</t>
+    <t>https://fbref.com/en/matches/f17f40e0/Palmeiras-Vasco-da-Gama-June-13-2024-Serie-A</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/930871d8/Bahia-Fortaleza-June-13-2024-Serie-A</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/f17f40e0/Palmeiras-Vasco-da-Gama-June-13-2024-Serie-A</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/307328b7/Red-Bull-Bragantino-Juventude-June-15-2024-Serie-A</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/46286d05/Classico-Majestoso-Corinthians-Sao-Paulo-June-16-2024-Serie-A</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/25aab3a0/Vitoria-Internacional-June-16-2024-Serie-A</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/46286d05/Classico-Majestoso-Corinthians-Sao-Paulo-June-16-2024-Serie-A</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/64a04e10/Athletico-Paranaense-Flamengo-June-16-2024-Serie-A</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/4ebfaebd/Cuiaba-Fortaleza-June-16-2024-Serie-A</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/a9931e51/Vasco-da-Gama-Cruzeiro-June-16-2024-Serie-A</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/391366f7/Criciuma-Bahia-June-16-2024-Serie-A</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/4257cbc2/Gremio-Botafogo-RJ-June-16-2024-Serie-A</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/a9931e51/Vasco-da-Gama-Cruzeiro-June-16-2024-Serie-A</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/29cda5d2/Fluminense-Atletico-Goianiense-June-15-2024-Serie-A</t>
   </si>
   <si>
@@ -1004,15 +1418,15 @@
     <t>https://fbref.com/en/matches/9c325553/Botafogo-RJ-Athletico-Paranaense-June-19-2024-Serie-A</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/d0569570/Juventude-Vasco-da-Gama-June-19-2024-Serie-A</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/081091ac/Fortaleza-Gremio-June-19-2024-Serie-A</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/a63c79b5/Sao-Paulo-Cuiaba-June-19-2024-Serie-A</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/d0569570/Juventude-Vasco-da-Gama-June-19-2024-Serie-A</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/30eb9fe9/Vitoria-Atletico-Mineiro-June-20-2024-Serie-A</t>
   </si>
   <si>
@@ -1040,21 +1454,21 @@
     <t>https://fbref.com/en/matches/2710ddc4/Fluminense-Flamengo-June-23-2024-Serie-A</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/9f68e36c/Athletico-Paranaense-Corinthians-June-23-2024-Serie-A</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/4afab374/Bahia-Cruzeiro-June-23-2024-Serie-A</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/9f68e36c/Athletico-Paranaense-Corinthians-June-23-2024-Serie-A</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/31001bc3/Atletico-Mineiro-Fortaleza-June-23-2024-Serie-A</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/93b80bf5/Red-Bull-Bragantino-Vitoria-June-23-2024-Serie-A</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/6c5678df/Palmeiras-Juventude-June-23-2024-Serie-A</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/93b80bf5/Red-Bull-Bragantino-Vitoria-June-23-2024-Serie-A</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/57771a62/Vasco-da-Gama-Sao-Paulo-June-22-2024-Serie-A</t>
   </si>
   <si>
@@ -1064,30 +1478,30 @@
     <t>https://fbref.com/en/matches/83e0aea0/Cruzeiro-Athletico-Paranaense-June-26-2024-Serie-A</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/7ff3c7d6/Corinthians-Cuiaba-June-26-2024-Serie-A</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/0fd769cc/Juventude-Flamengo-June-26-2024-Serie-A</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/4ad7fbcc/Atletico-Goianiense-Gremio-June-26-2024-Serie-A</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/7ff3c7d6/Corinthians-Cuiaba-June-26-2024-Serie-A</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/a15030a1/Fluminense-Vitoria-June-27-2024-Serie-A</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/0f056001/Sao-Paulo-Criciuma-June-27-2024-Serie-A</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/2895ef08/Internacional-Atletico-Mineiro-June-26-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/ec9e81b1/Fortaleza-Palmeiras-June-26-2024-Serie-A</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/0d6673b1/Bahia-Vasco-da-Gama-June-26-2024-Serie-A</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/2895ef08/Internacional-Atletico-Mineiro-June-26-2024-Serie-A</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/ec9e81b1/Fortaleza-Palmeiras-June-26-2024-Serie-A</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/44acb90c/Cuiaba-Red-Bull-Bragantino-June-29-2024-Serie-A</t>
   </si>
   <si>
@@ -1097,24 +1511,24 @@
     <t>https://fbref.com/en/matches/56af3243/Atletico-Mineiro-Atletico-Goianiense-June-30-2024-Serie-A</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/a8d11509/Gremio-Fluminense-June-30-2024-Serie-A</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/4556317d/Sao-Paulo-Bahia-June-30-2024-Serie-A</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/7f6df1bb/Fortaleza-Juventude-June-30-2024-Serie-A</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/a8d11509/Gremio-Fluminense-June-30-2024-Serie-A</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/8b8dd0f5/Flamengo-Cruzeiro-June-30-2024-Serie-A</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/c0218242/Vitoria-Athletico-Paranaense-June-30-2024-Serie-A</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/9f18fad7/Criciuma-Internacional-June-30-2024-Serie-A</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/c0218242/Vitoria-Athletico-Paranaense-June-30-2024-Serie-A</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/e89f509a/Palmeiras-Corinthians-July-1-2024-Serie-A</t>
   </si>
   <si>
@@ -1133,60 +1547,60 @@
     <t>https://fbref.com/en/matches/c529021c/Bahia-Juventude-July-4-2024-Serie-A</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/db28e378/Fluminense-Internacional-July-4-2024-Serie-A</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/c7f01a78/Corinthians-Vitoria-July-4-2024-Serie-A</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/db28e378/Fluminense-Internacional-July-4-2024-Serie-A</t>
+    <t>https://fbref.com/en/matches/981e26b6/Red-Bull-Bragantino-Atletico-Goianiense-July-3-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/dd8e8da8/Atletico-Mineiro-Flamengo-July-3-2024-Serie-A</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/5d6f4b6b/Athletico-Paranaense-Sao-Paulo-July-3-2024-Serie-A</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/981e26b6/Red-Bull-Bragantino-Atletico-Goianiense-July-3-2024-Serie-A</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/dd8e8da8/Atletico-Mineiro-Flamengo-July-3-2024-Serie-A</t>
+    <t>https://fbref.com/en/matches/86a1d64d/Sao-Paulo-Red-Bull-Bragantino-July-6-2024-Serie-A</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/26310ed9/Flamengo-Cuiaba-July-6-2024-Serie-A</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/86a1d64d/Sao-Paulo-Red-Bull-Bragantino-July-6-2024-Serie-A</t>
+    <t>https://fbref.com/en/matches/a150942f/Juventude-Gremio-July-7-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/ddff9788/Cruzeiro-Corinthians-July-7-2024-Serie-A</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/3672f0cf/Fortaleza-Fluminense-July-7-2024-Serie-A</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/a150942f/Juventude-Gremio-July-7-2024-Serie-A</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/ddff9788/Cruzeiro-Corinthians-July-7-2024-Serie-A</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/463057f1/Internacional-Vasco-da-Gama-July-7-2024-Serie-A</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/c4d413bf/Atletico-Goianiense-Athletico-Paranaense-July-7-2024-Serie-A</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/e777d3dc/Vitoria-Criciuma-July-7-2024-Serie-A</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/cf1bcd5e/Palmeiras-Bahia-July-7-2024-Serie-A</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/e777d3dc/Vitoria-Criciuma-July-7-2024-Serie-A</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/76d329cb/Botafogo-RJ-Atletico-Mineiro-July-7-2024-Serie-A</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/5b7823ea/Gremio-Cruzeiro-July-10-2024-Serie-A</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/f260927e/Vasco-da-Gama-Corinthians-July-10-2024-Serie-A</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/2330ae6e/Athletico-Paranaense-Bahia-July-10-2024-Serie-A</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/f260927e/Vasco-da-Gama-Corinthians-July-10-2024-Serie-A</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/0523260c/Palmeiras-Atletico-Goianiense-July-11-2024-Serie-A</t>
   </si>
   <si>
@@ -1220,12 +1634,12 @@
     <t>https://fbref.com/en/matches/4e96eb28/Corinthians-Criciuma-July-16-2024-Serie-A</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/f2802382/Botafogo-RJ-Palmeiras-July-17-2024-Serie-A</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/d828c590/Fortaleza-Vitoria-July-17-2024-Serie-A</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/f2802382/Botafogo-RJ-Palmeiras-July-17-2024-Serie-A</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/7aa9d167/Flamengo-Criciuma-July-20-2024-Serie-A</t>
   </si>
   <si>
@@ -1241,15 +1655,15 @@
     <t>https://fbref.com/en/matches/57c57174/Atletico-Mineiro-Vasco-da-Gama-July-21-2024-Serie-A</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/e4fcb89c/Juventude-Sao-Paulo-July-21-2024-Serie-A</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/658eff3c/Red-Bull-Bragantino-Athletico-Paranaense-July-21-2024-Serie-A</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/7ed52b26/Fortaleza-Atletico-Goianiense-July-21-2024-Serie-A</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/e4fcb89c/Juventude-Sao-Paulo-July-21-2024-Serie-A</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/cedc908c/Cuiaba-Fluminense-July-21-2024-Serie-A</t>
   </si>
   <si>
@@ -1271,18 +1685,18 @@
     <t>https://fbref.com/en/matches/00062d3c/Corinthians-Gremio-July-25-2024-Serie-A</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/fcb3a1d2/Fluminense-Palmeiras-July-24-2024-Serie-A</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/4718c1cd/Atletico-Goianiense-Bahia-July-24-2024-Serie-A</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/fcb3a1d2/Fluminense-Palmeiras-July-24-2024-Serie-A</t>
+    <t>https://fbref.com/en/matches/b4a136d6/Juventude-Criciuma-July-27-2024-Serie-A</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/884db190/Palmeiras-Vitoria-July-27-2024-Serie-A</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/b4a136d6/Juventude-Criciuma-July-27-2024-Serie-A</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/06a41b67/Bahia-Internacional-July-27-2024-Serie-A</t>
   </si>
   <si>
@@ -1319,15 +1733,15 @@
     <t>https://fbref.com/en/matches/e4bd97f5/Criciuma-Atletico-Mineiro-August-3-2024-Serie-A</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/8d8133f9/Corinthians-Juventude-August-4-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/e4136a2b/Athletico-Paranaense-Gremio-August-4-2024-Serie-A</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/84ad3b2c/Fluminense-Bahia-August-4-2024-Serie-A</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/8d8133f9/Corinthians-Juventude-August-4-2024-Serie-A</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/e4136a2b/Athletico-Paranaense-Gremio-August-4-2024-Serie-A</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/0ea5728b/Internacional-Palmeiras-August-4-2024-Serie-A</t>
   </si>
   <si>
@@ -1358,15 +1772,15 @@
     <t>https://fbref.com/en/matches/054386b8/Internacional-Athletico-Paranaense-August-11-2024-Serie-A</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/543a286f/Corinthians-Red-Bull-Bragantino-August-10-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/e8c91184/Vasco-da-Gama-Fluminense-August-10-2024-Serie-A</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/0da8aa4b/Cruzeiro-Atletico-Mineiro-August-10-2024-Serie-A</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/543a286f/Corinthians-Red-Bull-Bragantino-August-10-2024-Serie-A</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/e8c91184/Vasco-da-Gama-Fluminense-August-10-2024-Serie-A</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/9f6a7147/Internacional-Juventude-August-14-2024-Serie-A</t>
   </si>
   <si>
@@ -1388,12 +1802,12 @@
     <t>https://fbref.com/en/matches/917e890f/Atletico-Goianiense-Internacional-August-18-2024-Serie-A</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/ba80f8ac/Botafogo-RJ-Flamengo-August-18-2024-Serie-A</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/988ff3e3/Athletico-Paranaense-Juventude-August-18-2024-Serie-A</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/ba80f8ac/Botafogo-RJ-Flamengo-August-18-2024-Serie-A</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/abab024d/Fluminense-Corinthians-August-17-2024-Serie-A</t>
   </si>
   <si>
@@ -1406,15 +1820,15 @@
     <t>https://fbref.com/en/matches/693cf3cb/Palmeiras-Cuiaba-August-24-2024-Serie-A</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/c0a8d1ea/Fortaleza-Corinthians-August-25-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/7f4e3af4/Bahia-Botafogo-RJ-August-25-2024-Serie-A</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/16714502/Criciuma-Gremio-August-25-2024-Serie-A</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/7f4e3af4/Bahia-Botafogo-RJ-August-25-2024-Serie-A</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/c0a8d1ea/Fortaleza-Corinthians-August-25-2024-Serie-A</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/79532d5b/Sao-Paulo-Vitoria-August-25-2024-Serie-A</t>
   </si>
   <si>
@@ -1451,22 +1865,436 @@
     <t>https://fbref.com/en/matches/1d332259/Juventude-Internacional-September-1-2024-Serie-A</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/c9178fde/Vitoria-Vasco-da-Gama-September-1-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/ba9764f8/Fluminense-Sao-Paulo-September-1-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/fa27d6de/Red-Bull-Bragantino-Bahia-September-1-2024-Serie-A</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/9818b8f0/Athletico-Paranaense-Palmeiras-September-1-2024-Serie-A</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/ba9764f8/Fluminense-Sao-Paulo-September-1-2024-Serie-A</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/c9178fde/Vitoria-Vasco-da-Gama-September-1-2024-Serie-A</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/fa27d6de/Red-Bull-Bragantino-Bahia-September-1-2024-Serie-A</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/fe3afc8c/Botafogo-RJ-Fortaleza-August-31-2024-Serie-A</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/81ad2795/Cuiaba-Juventude-September-5-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/73b22908/Internacional-Fortaleza-September-11-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/669c6eec/Atletico-Goianiense-Vitoria-September-14-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/9ff2ccfb/Athletico-Paranaense-Fortaleza-September-14-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/f840653c/Palmeiras-Criciuma-September-15-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/25d75bfc/Red-Bull-Bragantino-Gremio-September-15-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/d78f88f7/Juventude-Fluminense-September-15-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/24766b1d/Cruzeiro-Sao-Paulo-September-15-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/19ccb168/Classico-dos-Milhoes-Flamengo-Vasco-da-Gama-September-15-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/95664a87/Bahia-Atletico-Mineiro-September-15-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/96c9cb35/Botafogo-RJ-Corinthians-September-14-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/d386688b/Internacional-Cuiaba-September-16-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/9b226572/Vitoria-Juventude-September-21-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/aa0683d1/Corinthians-Atletico-Goianiense-September-21-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/64deb2a0/Fluminense-Botafogo-RJ-September-21-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/cccfa1db/Vasco-da-Gama-Palmeiras-September-22-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/cd6767af/Atletico-Mineiro-Red-Bull-Bragantino-September-22-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/1c4268a0/Cuiaba-Cruzeiro-September-22-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/0a86cb63/Gremio-Flamengo-September-22-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/16602935/Sao-Paulo-Internacional-September-22-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/babc88a6/Criciuma-Athletico-Paranaense-September-22-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/0b1ee8dc/Fortaleza-Bahia-September-21-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/fbb40f13/Gremio-Criciuma-September-25-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/0e53bd28/Red-Bull-Bragantino-Internacional-September-25-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/b13912c8/Palmeiras-Atletico-Mineiro-September-28-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/71fc3558/Juventude-Red-Bull-Bragantino-September-29-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/4032bded/Fortaleza-Cuiaba-September-29-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/72e965ed/Atletico-Goianiense-Fluminense-September-29-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/ac52cacc/Classico-Majestoso-Sao-Paulo-Corinthians-September-29-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/b2e0b425/Bahia-Criciuma-September-29-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/7b02ac23/Internacional-Vitoria-September-29-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/26feb496/Cruzeiro-Vasco-da-Gama-September-29-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/b3539655/Flamengo-Athletico-Paranaense-September-29-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/6549c685/Botafogo-RJ-Gremio-September-28-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/2a9fef5e/Criciuma-Atletico-Goianiense-October-3-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/e780b2c5/Fluminense-Cruzeiro-October-3-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/5ec2a035/Red-Bull-Bragantino-Palmeiras-October-5-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/f759afc6/Atletico-Mineiro-Vitoria-October-5-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/a1af7d32/Athletico-Paranaense-Botafogo-RJ-October-5-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/50134ef5/Cuiaba-Sao-Paulo-October-5-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/95ed39b1/Bahia-Flamengo-October-5-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/2feabb9f/Corinthians-Internacional-October-5-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/986278fd/Gremio-Fortaleza-October-4-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/cc5acc66/Vasco-da-Gama-Juventude-October-5-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/d6af8ec8/Atletico-Mineiro-Gremio-October-9-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/41451949/Corinthians-Athletico-Paranaense-October-17-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/1a78d844/Flamengo-Fluminense-October-17-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/a6483dba/Fortaleza-Atletico-Mineiro-October-16-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/39edff54/Sao-Paulo-Vasco-da-Gama-October-16-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/b3663457/Atletico-Goianiense-Cuiaba-October-18-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/de6d29f6/Botafogo-RJ-Criciuma-October-18-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/df76c417/Internacional-Gremio-October-19-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/8f3cc7f6/Vitoria-Red-Bull-Bragantino-October-19-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/700c82e5/Cruzeiro-Bahia-October-18-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/60c5ef86/Juventude-Palmeiras-October-20-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/276c97ba/Fluminense-Athletico-Paranaense-October-22-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/25e9f47a/Vasco-da-Gama-Cuiaba-October-24-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/b865ec6e/Gremio-Atletico-Goianiense-October-26-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/6d7dfc03/Flamengo-Juventude-October-26-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/fdc22a21/Palmeiras-Fortaleza-October-26-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/63f7545e/Vitoria-Fluminense-October-26-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/382ad3ed/Athletico-Paranaense-Cruzeiro-October-26-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/65dcd691/Red-Bull-Bragantino-Botafogo-RJ-October-26-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/2abfb5cb/Atletico-Mineiro-Internacional-October-26-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/bf6faae7/Criciuma-Sao-Paulo-October-26-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/b5e89798/Cuiaba-Corinthians-October-28-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/f7071236/Vasco-da-Gama-Bahia-October-28-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/e4013ad4/Internacional-Flamengo-October-30-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/1a567820/Red-Bull-Bragantino-Cuiaba-November-2-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/9a68cbe5/Athletico-Paranaense-Vitoria-November-2-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/0a88f6a1/Juventude-Fortaleza-November-2-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/bb1a4828/Fluminense-Gremio-November-1-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/434b7e49/Corinthians-Palmeiras-November-4-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/47300243/Bahia-Sao-Paulo-November-5-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/53a8829c/Internacional-Criciuma-November-5-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/c19c6cca/Botafogo-RJ-Vasco-da-Gama-November-5-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/400101c1/Atletico-Goianiense-Atletico-Mineiro-November-6-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/e697d1ef/Cruzeiro-Flamengo-November-6-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/9109bac8/Internacional-Fluminense-November-8-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/5f669f77/Botafogo-RJ-Cuiaba-November-9-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/1b2335d8/Vitoria-Corinthians-November-9-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/1a930935/Fortaleza-Vasco-da-Gama-November-9-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/1811c11a/Cruzeiro-Criciuma-November-9-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/f4b8717f/Juventude-Bahia-November-9-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/24423a01/Atletico-Goianiense-Red-Bull-Bragantino-November-9-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/2f0c26e9/Palmeiras-Gremio-November-8-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/f47490cd/Sao-Paulo-Athletico-Paranaense-November-9-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/ee4ee1f9/Flamengo-Atletico-Mineiro-November-13-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/b2500302/Athletico-Paranaense-Atletico-Mineiro-November-16-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/b623212d/Corinthians-Cruzeiro-November-20-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/fc1334d5/Criciuma-Vitoria-November-20-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/0ff53c96/Athletico-Paranaense-Atletico-Goianiense-November-20-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/92f42356/Red-Bull-Bragantino-Sao-Paulo-November-20-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/dc88983e/Cuiaba-Flamengo-November-20-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/62543ab3/Bahia-Palmeiras-November-20-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/f42869fb/Gremio-Juventude-November-20-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/978962ea/Vasco-da-Gama-Internacional-November-21-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/7e6e4e83/Atletico-Mineiro-Botafogo-RJ-November-20-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/d535ac5e/Juventude-Cuiaba-November-23-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/c8eb71b9/Botafogo-RJ-Vitoria-November-23-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/b2033415/Atletico-Goianiense-Palmeiras-November-23-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/d8463264/Fluminense-Fortaleza-November-22-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/bd40427d/Internacional-Red-Bull-Bragantino-November-24-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/571b8b37/Bahia-Athletico-Paranaense-November-24-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/cc1dd787/Corinthians-Vasco-da-Gama-November-24-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/45170f90/Sao-Paulo-Atletico-Mineiro-November-23-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/9fa5da4b/Fluminense-Criciuma-November-26-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/45858d83/Fortaleza-Flamengo-November-26-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/9142d2e3/Palmeiras-Botafogo-RJ-November-26-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/032b9ca6/Atletico-Mineiro-Juventude-November-26-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/7018a87d/Cruzeiro-Gremio-November-27-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/b599d2d3/Cuiaba-Bahia-November-30-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/13053ece/Criciuma-Corinthians-November-30-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/ead06356/Flamengo-Internacional-December-1-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/e7873a69/Gremio-Sao-Paulo-December-1-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/06efb7e7/Vitoria-Fortaleza-December-1-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/bf19db63/Athletico-Paranaense-Fluminense-December-1-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/afbe1e36/Red-Bull-Bragantino-Cruzeiro-December-1-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/4ea19de8/Vasco-da-Gama-Atletico-Goianiense-November-30-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/0c167ff1/Corinthians-Bahia-December-3-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/ca1e8b16/Vasco-da-Gama-Atletico-Mineiro-December-4-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/8ce46e24/Criciuma-Flamengo-December-4-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/fd3cc006/Sao-Paulo-Juventude-December-4-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/aab0df7a/Vitoria-Gremio-December-4-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/d3d81805/Fluminense-Cuiaba-December-5-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/f52195c1/Athletico-Paranaense-Red-Bull-Bragantino-December-5-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/27d2f7b5/Atletico-Goianiense-Fortaleza-December-4-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/91f4f6e4/Internacional-Botafogo-RJ-December-4-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/99e0f3e5/Cruzeiro-Palmeiras-December-4-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/6b0dd4b5/Cuiaba-Vasco-da-Gama-December-8-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/c67693ce/Fortaleza-Internacional-December-8-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/63b8d3b7/Flamengo-Vitoria-December-8-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/c93b4ff3/Gremio-Corinthians-December-8-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/f4a35cc2/Juventude-Cruzeiro-December-8-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/fd4de3a4/Atletico-Mineiro-Athletico-Paranaense-December-8-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/cd242e5b/Palmeiras-Fluminense-December-8-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/eef876ea/Bahia-Atletico-Goianiense-December-8-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/7135693e/Red-Bull-Bragantino-Criciuma-December-8-2024-Serie-A</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/10b133fc/Botafogo-RJ-Sao-Paulo-December-8-2024-Serie-A</t>
   </si>
 </sst>
 </file>
@@ -1525,7 +2353,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>243</v>
+        <v>381</v>
       </c>
     </row>
     <row r="3">
@@ -1533,7 +2361,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>244</v>
+        <v>382</v>
       </c>
     </row>
     <row r="4">
@@ -1541,7 +2369,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>245</v>
+        <v>383</v>
       </c>
     </row>
     <row r="5">
@@ -1549,7 +2377,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>246</v>
+        <v>384</v>
       </c>
     </row>
     <row r="6">
@@ -1557,7 +2385,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>247</v>
+        <v>385</v>
       </c>
     </row>
     <row r="7">
@@ -1565,7 +2393,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>248</v>
+        <v>386</v>
       </c>
     </row>
     <row r="8">
@@ -1573,7 +2401,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>249</v>
+        <v>387</v>
       </c>
     </row>
     <row r="9">
@@ -1581,7 +2409,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>250</v>
+        <v>388</v>
       </c>
     </row>
     <row r="10">
@@ -1589,7 +2417,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>251</v>
+        <v>389</v>
       </c>
     </row>
     <row r="11">
@@ -1597,7 +2425,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>252</v>
+        <v>390</v>
       </c>
     </row>
     <row r="12">
@@ -1605,7 +2433,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>253</v>
+        <v>391</v>
       </c>
     </row>
     <row r="13">
@@ -1613,7 +2441,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>254</v>
+        <v>392</v>
       </c>
     </row>
     <row r="14">
@@ -1621,7 +2449,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>255</v>
+        <v>393</v>
       </c>
     </row>
     <row r="15">
@@ -1629,7 +2457,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>256</v>
+        <v>394</v>
       </c>
     </row>
     <row r="16">
@@ -1637,7 +2465,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>257</v>
+        <v>395</v>
       </c>
     </row>
     <row r="17">
@@ -1645,7 +2473,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>258</v>
+        <v>396</v>
       </c>
     </row>
     <row r="18">
@@ -1653,7 +2481,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>259</v>
+        <v>397</v>
       </c>
     </row>
     <row r="19">
@@ -1661,7 +2489,7 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>260</v>
+        <v>398</v>
       </c>
     </row>
     <row r="20">
@@ -1669,7 +2497,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>261</v>
+        <v>399</v>
       </c>
     </row>
     <row r="21">
@@ -1677,7 +2505,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>262</v>
+        <v>400</v>
       </c>
     </row>
     <row r="22">
@@ -1685,7 +2513,7 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>263</v>
+        <v>401</v>
       </c>
     </row>
     <row r="23">
@@ -1693,7 +2521,7 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>264</v>
+        <v>402</v>
       </c>
     </row>
     <row r="24">
@@ -1701,7 +2529,7 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>265</v>
+        <v>403</v>
       </c>
     </row>
     <row r="25">
@@ -1709,7 +2537,7 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>266</v>
+        <v>404</v>
       </c>
     </row>
     <row r="26">
@@ -1717,7 +2545,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>267</v>
+        <v>405</v>
       </c>
     </row>
     <row r="27">
@@ -1725,7 +2553,7 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>268</v>
+        <v>406</v>
       </c>
     </row>
     <row r="28">
@@ -1733,7 +2561,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>269</v>
+        <v>407</v>
       </c>
     </row>
     <row r="29">
@@ -1741,7 +2569,7 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>270</v>
+        <v>408</v>
       </c>
     </row>
     <row r="30">
@@ -1749,7 +2577,7 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>271</v>
+        <v>409</v>
       </c>
     </row>
     <row r="31">
@@ -1757,7 +2585,7 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>272</v>
+        <v>410</v>
       </c>
     </row>
     <row r="32">
@@ -1765,7 +2593,7 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>273</v>
+        <v>411</v>
       </c>
     </row>
     <row r="33">
@@ -1773,7 +2601,7 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>274</v>
+        <v>412</v>
       </c>
     </row>
     <row r="34">
@@ -1781,7 +2609,7 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>275</v>
+        <v>413</v>
       </c>
     </row>
     <row r="35">
@@ -1789,7 +2617,7 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>276</v>
+        <v>414</v>
       </c>
     </row>
     <row r="36">
@@ -1797,7 +2625,7 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>277</v>
+        <v>415</v>
       </c>
     </row>
     <row r="37">
@@ -1805,7 +2633,7 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>278</v>
+        <v>416</v>
       </c>
     </row>
     <row r="38">
@@ -1813,7 +2641,7 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>279</v>
+        <v>417</v>
       </c>
     </row>
     <row r="39">
@@ -1821,7 +2649,7 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>280</v>
+        <v>418</v>
       </c>
     </row>
     <row r="40">
@@ -1829,7 +2657,7 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>281</v>
+        <v>419</v>
       </c>
     </row>
     <row r="41">
@@ -1837,7 +2665,7 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>282</v>
+        <v>420</v>
       </c>
     </row>
     <row r="42">
@@ -1845,7 +2673,7 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>283</v>
+        <v>421</v>
       </c>
     </row>
     <row r="43">
@@ -1853,7 +2681,7 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>284</v>
+        <v>422</v>
       </c>
     </row>
     <row r="44">
@@ -1861,7 +2689,7 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>285</v>
+        <v>423</v>
       </c>
     </row>
     <row r="45">
@@ -1869,7 +2697,7 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>286</v>
+        <v>424</v>
       </c>
     </row>
     <row r="46">
@@ -1877,7 +2705,7 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>287</v>
+        <v>425</v>
       </c>
     </row>
     <row r="47">
@@ -1885,7 +2713,7 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>288</v>
+        <v>426</v>
       </c>
     </row>
     <row r="48">
@@ -1893,7 +2721,7 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>289</v>
+        <v>427</v>
       </c>
     </row>
     <row r="49">
@@ -1901,7 +2729,7 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>290</v>
+        <v>428</v>
       </c>
     </row>
     <row r="50">
@@ -1909,7 +2737,7 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>291</v>
+        <v>429</v>
       </c>
     </row>
     <row r="51">
@@ -1917,7 +2745,7 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>292</v>
+        <v>430</v>
       </c>
     </row>
     <row r="52">
@@ -1925,7 +2753,7 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>293</v>
+        <v>431</v>
       </c>
     </row>
     <row r="53">
@@ -1933,7 +2761,7 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>294</v>
+        <v>432</v>
       </c>
     </row>
     <row r="54">
@@ -1941,7 +2769,7 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>295</v>
+        <v>433</v>
       </c>
     </row>
     <row r="55">
@@ -1949,7 +2777,7 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>296</v>
+        <v>434</v>
       </c>
     </row>
     <row r="56">
@@ -1957,7 +2785,7 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>297</v>
+        <v>435</v>
       </c>
     </row>
     <row r="57">
@@ -1965,7 +2793,7 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>298</v>
+        <v>436</v>
       </c>
     </row>
     <row r="58">
@@ -1973,7 +2801,7 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>299</v>
+        <v>437</v>
       </c>
     </row>
     <row r="59">
@@ -1981,7 +2809,7 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>300</v>
+        <v>438</v>
       </c>
     </row>
     <row r="60">
@@ -1989,7 +2817,7 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>301</v>
+        <v>439</v>
       </c>
     </row>
     <row r="61">
@@ -1997,7 +2825,7 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>302</v>
+        <v>440</v>
       </c>
     </row>
     <row r="62">
@@ -2005,7 +2833,7 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>303</v>
+        <v>441</v>
       </c>
     </row>
     <row r="63">
@@ -2013,7 +2841,7 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>304</v>
+        <v>442</v>
       </c>
     </row>
     <row r="64">
@@ -2021,7 +2849,7 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>305</v>
+        <v>443</v>
       </c>
     </row>
     <row r="65">
@@ -2029,7 +2857,7 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>306</v>
+        <v>444</v>
       </c>
     </row>
     <row r="66">
@@ -2037,7 +2865,7 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>307</v>
+        <v>445</v>
       </c>
     </row>
     <row r="67">
@@ -2045,7 +2873,7 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>308</v>
+        <v>446</v>
       </c>
     </row>
     <row r="68">
@@ -2053,7 +2881,7 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>309</v>
+        <v>447</v>
       </c>
     </row>
     <row r="69">
@@ -2061,7 +2889,7 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>310</v>
+        <v>448</v>
       </c>
     </row>
     <row r="70">
@@ -2069,7 +2897,7 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>311</v>
+        <v>449</v>
       </c>
     </row>
     <row r="71">
@@ -2077,7 +2905,7 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>312</v>
+        <v>450</v>
       </c>
     </row>
     <row r="72">
@@ -2085,7 +2913,7 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>313</v>
+        <v>451</v>
       </c>
     </row>
     <row r="73">
@@ -2093,7 +2921,7 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>314</v>
+        <v>452</v>
       </c>
     </row>
     <row r="74">
@@ -2101,7 +2929,7 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>315</v>
+        <v>453</v>
       </c>
     </row>
     <row r="75">
@@ -2109,7 +2937,7 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>316</v>
+        <v>454</v>
       </c>
     </row>
     <row r="76">
@@ -2117,7 +2945,7 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>317</v>
+        <v>455</v>
       </c>
     </row>
     <row r="77">
@@ -2125,7 +2953,7 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>318</v>
+        <v>456</v>
       </c>
     </row>
     <row r="78">
@@ -2133,7 +2961,7 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>319</v>
+        <v>457</v>
       </c>
     </row>
     <row r="79">
@@ -2141,7 +2969,7 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>320</v>
+        <v>458</v>
       </c>
     </row>
     <row r="80">
@@ -2149,7 +2977,7 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>321</v>
+        <v>459</v>
       </c>
     </row>
     <row r="81">
@@ -2157,7 +2985,7 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>322</v>
+        <v>460</v>
       </c>
     </row>
     <row r="82">
@@ -2165,7 +2993,7 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>323</v>
+        <v>461</v>
       </c>
     </row>
     <row r="83">
@@ -2173,7 +3001,7 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>324</v>
+        <v>462</v>
       </c>
     </row>
     <row r="84">
@@ -2181,7 +3009,7 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>325</v>
+        <v>463</v>
       </c>
     </row>
     <row r="85">
@@ -2189,7 +3017,7 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>326</v>
+        <v>464</v>
       </c>
     </row>
     <row r="86">
@@ -2197,7 +3025,7 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>327</v>
+        <v>465</v>
       </c>
     </row>
     <row r="87">
@@ -2205,7 +3033,7 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>328</v>
+        <v>466</v>
       </c>
     </row>
     <row r="88">
@@ -2213,7 +3041,7 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>329</v>
+        <v>467</v>
       </c>
     </row>
     <row r="89">
@@ -2221,7 +3049,7 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>330</v>
+        <v>468</v>
       </c>
     </row>
     <row r="90">
@@ -2229,7 +3057,7 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>331</v>
+        <v>469</v>
       </c>
     </row>
     <row r="91">
@@ -2237,7 +3065,7 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>332</v>
+        <v>470</v>
       </c>
     </row>
     <row r="92">
@@ -2245,7 +3073,7 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>333</v>
+        <v>471</v>
       </c>
     </row>
     <row r="93">
@@ -2253,7 +3081,7 @@
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>334</v>
+        <v>472</v>
       </c>
     </row>
     <row r="94">
@@ -2261,7 +3089,7 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>335</v>
+        <v>473</v>
       </c>
     </row>
     <row r="95">
@@ -2269,7 +3097,7 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>336</v>
+        <v>474</v>
       </c>
     </row>
     <row r="96">
@@ -2277,7 +3105,7 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>337</v>
+        <v>475</v>
       </c>
     </row>
     <row r="97">
@@ -2285,7 +3113,7 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>338</v>
+        <v>476</v>
       </c>
     </row>
     <row r="98">
@@ -2293,7 +3121,7 @@
         <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>339</v>
+        <v>477</v>
       </c>
     </row>
     <row r="99">
@@ -2301,7 +3129,7 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>340</v>
+        <v>478</v>
       </c>
     </row>
     <row r="100">
@@ -2309,7 +3137,7 @@
         <v>99</v>
       </c>
       <c r="B100" t="s">
-        <v>341</v>
+        <v>479</v>
       </c>
     </row>
     <row r="101">
@@ -2317,7 +3145,7 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>342</v>
+        <v>480</v>
       </c>
     </row>
     <row r="102">
@@ -2325,7 +3153,7 @@
         <v>101</v>
       </c>
       <c r="B102" t="s">
-        <v>343</v>
+        <v>481</v>
       </c>
     </row>
     <row r="103">
@@ -2333,7 +3161,7 @@
         <v>102</v>
       </c>
       <c r="B103" t="s">
-        <v>344</v>
+        <v>482</v>
       </c>
     </row>
     <row r="104">
@@ -2341,7 +3169,7 @@
         <v>103</v>
       </c>
       <c r="B104" t="s">
-        <v>345</v>
+        <v>483</v>
       </c>
     </row>
     <row r="105">
@@ -2349,7 +3177,7 @@
         <v>104</v>
       </c>
       <c r="B105" t="s">
-        <v>346</v>
+        <v>484</v>
       </c>
     </row>
     <row r="106">
@@ -2357,7 +3185,7 @@
         <v>105</v>
       </c>
       <c r="B106" t="s">
-        <v>347</v>
+        <v>485</v>
       </c>
     </row>
     <row r="107">
@@ -2365,7 +3193,7 @@
         <v>106</v>
       </c>
       <c r="B107" t="s">
-        <v>348</v>
+        <v>486</v>
       </c>
     </row>
     <row r="108">
@@ -2373,7 +3201,7 @@
         <v>107</v>
       </c>
       <c r="B108" t="s">
-        <v>349</v>
+        <v>487</v>
       </c>
     </row>
     <row r="109">
@@ -2381,7 +3209,7 @@
         <v>108</v>
       </c>
       <c r="B109" t="s">
-        <v>350</v>
+        <v>488</v>
       </c>
     </row>
     <row r="110">
@@ -2389,7 +3217,7 @@
         <v>109</v>
       </c>
       <c r="B110" t="s">
-        <v>351</v>
+        <v>489</v>
       </c>
     </row>
     <row r="111">
@@ -2397,7 +3225,7 @@
         <v>110</v>
       </c>
       <c r="B111" t="s">
-        <v>352</v>
+        <v>490</v>
       </c>
     </row>
     <row r="112">
@@ -2405,7 +3233,7 @@
         <v>111</v>
       </c>
       <c r="B112" t="s">
-        <v>353</v>
+        <v>491</v>
       </c>
     </row>
     <row r="113">
@@ -2413,7 +3241,7 @@
         <v>112</v>
       </c>
       <c r="B113" t="s">
-        <v>354</v>
+        <v>492</v>
       </c>
     </row>
     <row r="114">
@@ -2421,7 +3249,7 @@
         <v>113</v>
       </c>
       <c r="B114" t="s">
-        <v>355</v>
+        <v>493</v>
       </c>
     </row>
     <row r="115">
@@ -2429,7 +3257,7 @@
         <v>114</v>
       </c>
       <c r="B115" t="s">
-        <v>356</v>
+        <v>494</v>
       </c>
     </row>
     <row r="116">
@@ -2437,7 +3265,7 @@
         <v>115</v>
       </c>
       <c r="B116" t="s">
-        <v>357</v>
+        <v>495</v>
       </c>
     </row>
     <row r="117">
@@ -2445,7 +3273,7 @@
         <v>116</v>
       </c>
       <c r="B117" t="s">
-        <v>358</v>
+        <v>496</v>
       </c>
     </row>
     <row r="118">
@@ -2453,7 +3281,7 @@
         <v>117</v>
       </c>
       <c r="B118" t="s">
-        <v>359</v>
+        <v>497</v>
       </c>
     </row>
     <row r="119">
@@ -2461,7 +3289,7 @@
         <v>118</v>
       </c>
       <c r="B119" t="s">
-        <v>360</v>
+        <v>498</v>
       </c>
     </row>
     <row r="120">
@@ -2469,7 +3297,7 @@
         <v>119</v>
       </c>
       <c r="B120" t="s">
-        <v>361</v>
+        <v>499</v>
       </c>
     </row>
     <row r="121">
@@ -2477,7 +3305,7 @@
         <v>120</v>
       </c>
       <c r="B121" t="s">
-        <v>362</v>
+        <v>500</v>
       </c>
     </row>
     <row r="122">
@@ -2485,7 +3313,7 @@
         <v>121</v>
       </c>
       <c r="B122" t="s">
-        <v>363</v>
+        <v>501</v>
       </c>
     </row>
     <row r="123">
@@ -2493,7 +3321,7 @@
         <v>122</v>
       </c>
       <c r="B123" t="s">
-        <v>364</v>
+        <v>502</v>
       </c>
     </row>
     <row r="124">
@@ -2501,7 +3329,7 @@
         <v>123</v>
       </c>
       <c r="B124" t="s">
-        <v>365</v>
+        <v>503</v>
       </c>
     </row>
     <row r="125">
@@ -2509,7 +3337,7 @@
         <v>124</v>
       </c>
       <c r="B125" t="s">
-        <v>366</v>
+        <v>504</v>
       </c>
     </row>
     <row r="126">
@@ -2517,7 +3345,7 @@
         <v>125</v>
       </c>
       <c r="B126" t="s">
-        <v>367</v>
+        <v>505</v>
       </c>
     </row>
     <row r="127">
@@ -2525,7 +3353,7 @@
         <v>126</v>
       </c>
       <c r="B127" t="s">
-        <v>368</v>
+        <v>506</v>
       </c>
     </row>
     <row r="128">
@@ -2533,7 +3361,7 @@
         <v>127</v>
       </c>
       <c r="B128" t="s">
-        <v>369</v>
+        <v>507</v>
       </c>
     </row>
     <row r="129">
@@ -2541,7 +3369,7 @@
         <v>128</v>
       </c>
       <c r="B129" t="s">
-        <v>370</v>
+        <v>508</v>
       </c>
     </row>
     <row r="130">
@@ -2549,7 +3377,7 @@
         <v>129</v>
       </c>
       <c r="B130" t="s">
-        <v>371</v>
+        <v>509</v>
       </c>
     </row>
     <row r="131">
@@ -2557,7 +3385,7 @@
         <v>130</v>
       </c>
       <c r="B131" t="s">
-        <v>372</v>
+        <v>510</v>
       </c>
     </row>
     <row r="132">
@@ -2565,7 +3393,7 @@
         <v>131</v>
       </c>
       <c r="B132" t="s">
-        <v>373</v>
+        <v>511</v>
       </c>
     </row>
     <row r="133">
@@ -2573,7 +3401,7 @@
         <v>132</v>
       </c>
       <c r="B133" t="s">
-        <v>374</v>
+        <v>512</v>
       </c>
     </row>
     <row r="134">
@@ -2581,7 +3409,7 @@
         <v>133</v>
       </c>
       <c r="B134" t="s">
-        <v>375</v>
+        <v>513</v>
       </c>
     </row>
     <row r="135">
@@ -2589,7 +3417,7 @@
         <v>134</v>
       </c>
       <c r="B135" t="s">
-        <v>376</v>
+        <v>514</v>
       </c>
     </row>
     <row r="136">
@@ -2597,7 +3425,7 @@
         <v>135</v>
       </c>
       <c r="B136" t="s">
-        <v>377</v>
+        <v>515</v>
       </c>
     </row>
     <row r="137">
@@ -2605,7 +3433,7 @@
         <v>136</v>
       </c>
       <c r="B137" t="s">
-        <v>378</v>
+        <v>516</v>
       </c>
     </row>
     <row r="138">
@@ -2613,7 +3441,7 @@
         <v>137</v>
       </c>
       <c r="B138" t="s">
-        <v>379</v>
+        <v>517</v>
       </c>
     </row>
     <row r="139">
@@ -2621,7 +3449,7 @@
         <v>138</v>
       </c>
       <c r="B139" t="s">
-        <v>380</v>
+        <v>518</v>
       </c>
     </row>
     <row r="140">
@@ -2629,7 +3457,7 @@
         <v>139</v>
       </c>
       <c r="B140" t="s">
-        <v>381</v>
+        <v>519</v>
       </c>
     </row>
     <row r="141">
@@ -2637,7 +3465,7 @@
         <v>140</v>
       </c>
       <c r="B141" t="s">
-        <v>382</v>
+        <v>520</v>
       </c>
     </row>
     <row r="142">
@@ -2645,7 +3473,7 @@
         <v>141</v>
       </c>
       <c r="B142" t="s">
-        <v>383</v>
+        <v>521</v>
       </c>
     </row>
     <row r="143">
@@ -2653,7 +3481,7 @@
         <v>142</v>
       </c>
       <c r="B143" t="s">
-        <v>384</v>
+        <v>522</v>
       </c>
     </row>
     <row r="144">
@@ -2661,7 +3489,7 @@
         <v>143</v>
       </c>
       <c r="B144" t="s">
-        <v>385</v>
+        <v>523</v>
       </c>
     </row>
     <row r="145">
@@ -2669,7 +3497,7 @@
         <v>144</v>
       </c>
       <c r="B145" t="s">
-        <v>386</v>
+        <v>524</v>
       </c>
     </row>
     <row r="146">
@@ -2677,7 +3505,7 @@
         <v>145</v>
       </c>
       <c r="B146" t="s">
-        <v>387</v>
+        <v>525</v>
       </c>
     </row>
     <row r="147">
@@ -2685,7 +3513,7 @@
         <v>146</v>
       </c>
       <c r="B147" t="s">
-        <v>388</v>
+        <v>526</v>
       </c>
     </row>
     <row r="148">
@@ -2693,7 +3521,7 @@
         <v>147</v>
       </c>
       <c r="B148" t="s">
-        <v>389</v>
+        <v>527</v>
       </c>
     </row>
     <row r="149">
@@ -2701,7 +3529,7 @@
         <v>148</v>
       </c>
       <c r="B149" t="s">
-        <v>390</v>
+        <v>528</v>
       </c>
     </row>
     <row r="150">
@@ -2709,7 +3537,7 @@
         <v>149</v>
       </c>
       <c r="B150" t="s">
-        <v>391</v>
+        <v>529</v>
       </c>
     </row>
     <row r="151">
@@ -2717,7 +3545,7 @@
         <v>150</v>
       </c>
       <c r="B151" t="s">
-        <v>392</v>
+        <v>530</v>
       </c>
     </row>
     <row r="152">
@@ -2725,7 +3553,7 @@
         <v>151</v>
       </c>
       <c r="B152" t="s">
-        <v>393</v>
+        <v>531</v>
       </c>
     </row>
     <row r="153">
@@ -2733,7 +3561,7 @@
         <v>152</v>
       </c>
       <c r="B153" t="s">
-        <v>394</v>
+        <v>532</v>
       </c>
     </row>
     <row r="154">
@@ -2741,7 +3569,7 @@
         <v>153</v>
       </c>
       <c r="B154" t="s">
-        <v>395</v>
+        <v>533</v>
       </c>
     </row>
     <row r="155">
@@ -2749,7 +3577,7 @@
         <v>154</v>
       </c>
       <c r="B155" t="s">
-        <v>396</v>
+        <v>534</v>
       </c>
     </row>
     <row r="156">
@@ -2757,7 +3585,7 @@
         <v>155</v>
       </c>
       <c r="B156" t="s">
-        <v>397</v>
+        <v>535</v>
       </c>
     </row>
     <row r="157">
@@ -2765,7 +3593,7 @@
         <v>156</v>
       </c>
       <c r="B157" t="s">
-        <v>398</v>
+        <v>536</v>
       </c>
     </row>
     <row r="158">
@@ -2773,7 +3601,7 @@
         <v>157</v>
       </c>
       <c r="B158" t="s">
-        <v>399</v>
+        <v>537</v>
       </c>
     </row>
     <row r="159">
@@ -2781,7 +3609,7 @@
         <v>158</v>
       </c>
       <c r="B159" t="s">
-        <v>400</v>
+        <v>538</v>
       </c>
     </row>
     <row r="160">
@@ -2789,7 +3617,7 @@
         <v>159</v>
       </c>
       <c r="B160" t="s">
-        <v>401</v>
+        <v>539</v>
       </c>
     </row>
     <row r="161">
@@ -2797,7 +3625,7 @@
         <v>160</v>
       </c>
       <c r="B161" t="s">
-        <v>402</v>
+        <v>540</v>
       </c>
     </row>
     <row r="162">
@@ -2805,7 +3633,7 @@
         <v>161</v>
       </c>
       <c r="B162" t="s">
-        <v>403</v>
+        <v>541</v>
       </c>
     </row>
     <row r="163">
@@ -2813,7 +3641,7 @@
         <v>162</v>
       </c>
       <c r="B163" t="s">
-        <v>404</v>
+        <v>542</v>
       </c>
     </row>
     <row r="164">
@@ -2821,7 +3649,7 @@
         <v>163</v>
       </c>
       <c r="B164" t="s">
-        <v>405</v>
+        <v>543</v>
       </c>
     </row>
     <row r="165">
@@ -2829,7 +3657,7 @@
         <v>164</v>
       </c>
       <c r="B165" t="s">
-        <v>406</v>
+        <v>544</v>
       </c>
     </row>
     <row r="166">
@@ -2837,7 +3665,7 @@
         <v>165</v>
       </c>
       <c r="B166" t="s">
-        <v>407</v>
+        <v>545</v>
       </c>
     </row>
     <row r="167">
@@ -2845,7 +3673,7 @@
         <v>166</v>
       </c>
       <c r="B167" t="s">
-        <v>408</v>
+        <v>546</v>
       </c>
     </row>
     <row r="168">
@@ -2853,7 +3681,7 @@
         <v>167</v>
       </c>
       <c r="B168" t="s">
-        <v>409</v>
+        <v>547</v>
       </c>
     </row>
     <row r="169">
@@ -2861,7 +3689,7 @@
         <v>168</v>
       </c>
       <c r="B169" t="s">
-        <v>410</v>
+        <v>548</v>
       </c>
     </row>
     <row r="170">
@@ -2869,7 +3697,7 @@
         <v>169</v>
       </c>
       <c r="B170" t="s">
-        <v>411</v>
+        <v>549</v>
       </c>
     </row>
     <row r="171">
@@ -2877,7 +3705,7 @@
         <v>170</v>
       </c>
       <c r="B171" t="s">
-        <v>412</v>
+        <v>550</v>
       </c>
     </row>
     <row r="172">
@@ -2885,7 +3713,7 @@
         <v>171</v>
       </c>
       <c r="B172" t="s">
-        <v>413</v>
+        <v>551</v>
       </c>
     </row>
     <row r="173">
@@ -2893,7 +3721,7 @@
         <v>172</v>
       </c>
       <c r="B173" t="s">
-        <v>414</v>
+        <v>552</v>
       </c>
     </row>
     <row r="174">
@@ -2901,7 +3729,7 @@
         <v>173</v>
       </c>
       <c r="B174" t="s">
-        <v>415</v>
+        <v>553</v>
       </c>
     </row>
     <row r="175">
@@ -2909,7 +3737,7 @@
         <v>174</v>
       </c>
       <c r="B175" t="s">
-        <v>416</v>
+        <v>554</v>
       </c>
     </row>
     <row r="176">
@@ -2917,7 +3745,7 @@
         <v>175</v>
       </c>
       <c r="B176" t="s">
-        <v>417</v>
+        <v>555</v>
       </c>
     </row>
     <row r="177">
@@ -2925,7 +3753,7 @@
         <v>176</v>
       </c>
       <c r="B177" t="s">
-        <v>418</v>
+        <v>556</v>
       </c>
     </row>
     <row r="178">
@@ -2933,7 +3761,7 @@
         <v>177</v>
       </c>
       <c r="B178" t="s">
-        <v>419</v>
+        <v>557</v>
       </c>
     </row>
     <row r="179">
@@ -2941,7 +3769,7 @@
         <v>178</v>
       </c>
       <c r="B179" t="s">
-        <v>420</v>
+        <v>558</v>
       </c>
     </row>
     <row r="180">
@@ -2949,7 +3777,7 @@
         <v>179</v>
       </c>
       <c r="B180" t="s">
-        <v>421</v>
+        <v>559</v>
       </c>
     </row>
     <row r="181">
@@ -2957,7 +3785,7 @@
         <v>180</v>
       </c>
       <c r="B181" t="s">
-        <v>422</v>
+        <v>560</v>
       </c>
     </row>
     <row r="182">
@@ -2965,7 +3793,7 @@
         <v>181</v>
       </c>
       <c r="B182" t="s">
-        <v>423</v>
+        <v>561</v>
       </c>
     </row>
     <row r="183">
@@ -2973,7 +3801,7 @@
         <v>182</v>
       </c>
       <c r="B183" t="s">
-        <v>424</v>
+        <v>562</v>
       </c>
     </row>
     <row r="184">
@@ -2981,7 +3809,7 @@
         <v>183</v>
       </c>
       <c r="B184" t="s">
-        <v>425</v>
+        <v>563</v>
       </c>
     </row>
     <row r="185">
@@ -2989,7 +3817,7 @@
         <v>184</v>
       </c>
       <c r="B185" t="s">
-        <v>426</v>
+        <v>564</v>
       </c>
     </row>
     <row r="186">
@@ -2997,7 +3825,7 @@
         <v>185</v>
       </c>
       <c r="B186" t="s">
-        <v>427</v>
+        <v>565</v>
       </c>
     </row>
     <row r="187">
@@ -3005,7 +3833,7 @@
         <v>186</v>
       </c>
       <c r="B187" t="s">
-        <v>428</v>
+        <v>566</v>
       </c>
     </row>
     <row r="188">
@@ -3013,7 +3841,7 @@
         <v>187</v>
       </c>
       <c r="B188" t="s">
-        <v>429</v>
+        <v>567</v>
       </c>
     </row>
     <row r="189">
@@ -3021,7 +3849,7 @@
         <v>188</v>
       </c>
       <c r="B189" t="s">
-        <v>430</v>
+        <v>568</v>
       </c>
     </row>
     <row r="190">
@@ -3029,7 +3857,7 @@
         <v>189</v>
       </c>
       <c r="B190" t="s">
-        <v>431</v>
+        <v>569</v>
       </c>
     </row>
     <row r="191">
@@ -3037,7 +3865,7 @@
         <v>190</v>
       </c>
       <c r="B191" t="s">
-        <v>432</v>
+        <v>570</v>
       </c>
     </row>
     <row r="192">
@@ -3045,7 +3873,7 @@
         <v>191</v>
       </c>
       <c r="B192" t="s">
-        <v>433</v>
+        <v>571</v>
       </c>
     </row>
     <row r="193">
@@ -3053,7 +3881,7 @@
         <v>192</v>
       </c>
       <c r="B193" t="s">
-        <v>434</v>
+        <v>572</v>
       </c>
     </row>
     <row r="194">
@@ -3061,7 +3889,7 @@
         <v>193</v>
       </c>
       <c r="B194" t="s">
-        <v>435</v>
+        <v>573</v>
       </c>
     </row>
     <row r="195">
@@ -3069,7 +3897,7 @@
         <v>194</v>
       </c>
       <c r="B195" t="s">
-        <v>436</v>
+        <v>574</v>
       </c>
     </row>
     <row r="196">
@@ -3077,7 +3905,7 @@
         <v>195</v>
       </c>
       <c r="B196" t="s">
-        <v>437</v>
+        <v>575</v>
       </c>
     </row>
     <row r="197">
@@ -3085,7 +3913,7 @@
         <v>196</v>
       </c>
       <c r="B197" t="s">
-        <v>438</v>
+        <v>576</v>
       </c>
     </row>
     <row r="198">
@@ -3093,7 +3921,7 @@
         <v>197</v>
       </c>
       <c r="B198" t="s">
-        <v>439</v>
+        <v>577</v>
       </c>
     </row>
     <row r="199">
@@ -3101,7 +3929,7 @@
         <v>198</v>
       </c>
       <c r="B199" t="s">
-        <v>440</v>
+        <v>578</v>
       </c>
     </row>
     <row r="200">
@@ -3109,7 +3937,7 @@
         <v>199</v>
       </c>
       <c r="B200" t="s">
-        <v>441</v>
+        <v>579</v>
       </c>
     </row>
     <row r="201">
@@ -3117,7 +3945,7 @@
         <v>200</v>
       </c>
       <c r="B201" t="s">
-        <v>442</v>
+        <v>580</v>
       </c>
     </row>
     <row r="202">
@@ -3125,7 +3953,7 @@
         <v>201</v>
       </c>
       <c r="B202" t="s">
-        <v>443</v>
+        <v>581</v>
       </c>
     </row>
     <row r="203">
@@ -3133,7 +3961,7 @@
         <v>202</v>
       </c>
       <c r="B203" t="s">
-        <v>444</v>
+        <v>582</v>
       </c>
     </row>
     <row r="204">
@@ -3141,7 +3969,7 @@
         <v>203</v>
       </c>
       <c r="B204" t="s">
-        <v>445</v>
+        <v>583</v>
       </c>
     </row>
     <row r="205">
@@ -3149,7 +3977,7 @@
         <v>204</v>
       </c>
       <c r="B205" t="s">
-        <v>446</v>
+        <v>584</v>
       </c>
     </row>
     <row r="206">
@@ -3157,7 +3985,7 @@
         <v>205</v>
       </c>
       <c r="B206" t="s">
-        <v>447</v>
+        <v>585</v>
       </c>
     </row>
     <row r="207">
@@ -3165,7 +3993,7 @@
         <v>206</v>
       </c>
       <c r="B207" t="s">
-        <v>448</v>
+        <v>586</v>
       </c>
     </row>
     <row r="208">
@@ -3173,7 +4001,7 @@
         <v>207</v>
       </c>
       <c r="B208" t="s">
-        <v>449</v>
+        <v>587</v>
       </c>
     </row>
     <row r="209">
@@ -3181,7 +4009,7 @@
         <v>208</v>
       </c>
       <c r="B209" t="s">
-        <v>450</v>
+        <v>588</v>
       </c>
     </row>
     <row r="210">
@@ -3189,7 +4017,7 @@
         <v>209</v>
       </c>
       <c r="B210" t="s">
-        <v>451</v>
+        <v>589</v>
       </c>
     </row>
     <row r="211">
@@ -3197,7 +4025,7 @@
         <v>210</v>
       </c>
       <c r="B211" t="s">
-        <v>452</v>
+        <v>590</v>
       </c>
     </row>
     <row r="212">
@@ -3205,7 +4033,7 @@
         <v>211</v>
       </c>
       <c r="B212" t="s">
-        <v>453</v>
+        <v>591</v>
       </c>
     </row>
     <row r="213">
@@ -3213,7 +4041,7 @@
         <v>212</v>
       </c>
       <c r="B213" t="s">
-        <v>454</v>
+        <v>592</v>
       </c>
     </row>
     <row r="214">
@@ -3221,7 +4049,7 @@
         <v>213</v>
       </c>
       <c r="B214" t="s">
-        <v>455</v>
+        <v>593</v>
       </c>
     </row>
     <row r="215">
@@ -3229,7 +4057,7 @@
         <v>214</v>
       </c>
       <c r="B215" t="s">
-        <v>456</v>
+        <v>594</v>
       </c>
     </row>
     <row r="216">
@@ -3237,7 +4065,7 @@
         <v>215</v>
       </c>
       <c r="B216" t="s">
-        <v>457</v>
+        <v>595</v>
       </c>
     </row>
     <row r="217">
@@ -3245,7 +4073,7 @@
         <v>216</v>
       </c>
       <c r="B217" t="s">
-        <v>458</v>
+        <v>596</v>
       </c>
     </row>
     <row r="218">
@@ -3253,7 +4081,7 @@
         <v>217</v>
       </c>
       <c r="B218" t="s">
-        <v>459</v>
+        <v>597</v>
       </c>
     </row>
     <row r="219">
@@ -3261,7 +4089,7 @@
         <v>218</v>
       </c>
       <c r="B219" t="s">
-        <v>460</v>
+        <v>598</v>
       </c>
     </row>
     <row r="220">
@@ -3269,7 +4097,7 @@
         <v>219</v>
       </c>
       <c r="B220" t="s">
-        <v>461</v>
+        <v>599</v>
       </c>
     </row>
     <row r="221">
@@ -3277,7 +4105,7 @@
         <v>220</v>
       </c>
       <c r="B221" t="s">
-        <v>462</v>
+        <v>600</v>
       </c>
     </row>
     <row r="222">
@@ -3285,7 +4113,7 @@
         <v>221</v>
       </c>
       <c r="B222" t="s">
-        <v>463</v>
+        <v>601</v>
       </c>
     </row>
     <row r="223">
@@ -3293,7 +4121,7 @@
         <v>222</v>
       </c>
       <c r="B223" t="s">
-        <v>464</v>
+        <v>602</v>
       </c>
     </row>
     <row r="224">
@@ -3301,7 +4129,7 @@
         <v>223</v>
       </c>
       <c r="B224" t="s">
-        <v>465</v>
+        <v>603</v>
       </c>
     </row>
     <row r="225">
@@ -3309,7 +4137,7 @@
         <v>224</v>
       </c>
       <c r="B225" t="s">
-        <v>466</v>
+        <v>604</v>
       </c>
     </row>
     <row r="226">
@@ -3317,7 +4145,7 @@
         <v>225</v>
       </c>
       <c r="B226" t="s">
-        <v>467</v>
+        <v>605</v>
       </c>
     </row>
     <row r="227">
@@ -3325,7 +4153,7 @@
         <v>226</v>
       </c>
       <c r="B227" t="s">
-        <v>468</v>
+        <v>606</v>
       </c>
     </row>
     <row r="228">
@@ -3333,7 +4161,7 @@
         <v>227</v>
       </c>
       <c r="B228" t="s">
-        <v>469</v>
+        <v>607</v>
       </c>
     </row>
     <row r="229">
@@ -3341,7 +4169,7 @@
         <v>228</v>
       </c>
       <c r="B229" t="s">
-        <v>470</v>
+        <v>608</v>
       </c>
     </row>
     <row r="230">
@@ -3349,7 +4177,7 @@
         <v>229</v>
       </c>
       <c r="B230" t="s">
-        <v>471</v>
+        <v>609</v>
       </c>
     </row>
     <row r="231">
@@ -3357,7 +4185,7 @@
         <v>230</v>
       </c>
       <c r="B231" t="s">
-        <v>472</v>
+        <v>610</v>
       </c>
     </row>
     <row r="232">
@@ -3365,7 +4193,7 @@
         <v>231</v>
       </c>
       <c r="B232" t="s">
-        <v>473</v>
+        <v>611</v>
       </c>
     </row>
     <row r="233">
@@ -3373,7 +4201,7 @@
         <v>232</v>
       </c>
       <c r="B233" t="s">
-        <v>474</v>
+        <v>612</v>
       </c>
     </row>
     <row r="234">
@@ -3381,7 +4209,7 @@
         <v>233</v>
       </c>
       <c r="B234" t="s">
-        <v>475</v>
+        <v>613</v>
       </c>
     </row>
     <row r="235">
@@ -3389,7 +4217,7 @@
         <v>234</v>
       </c>
       <c r="B235" t="s">
-        <v>476</v>
+        <v>614</v>
       </c>
     </row>
     <row r="236">
@@ -3397,7 +4225,7 @@
         <v>235</v>
       </c>
       <c r="B236" t="s">
-        <v>477</v>
+        <v>615</v>
       </c>
     </row>
     <row r="237">
@@ -3405,7 +4233,7 @@
         <v>236</v>
       </c>
       <c r="B237" t="s">
-        <v>478</v>
+        <v>616</v>
       </c>
     </row>
     <row r="238">
@@ -3413,7 +4241,7 @@
         <v>237</v>
       </c>
       <c r="B238" t="s">
-        <v>479</v>
+        <v>617</v>
       </c>
     </row>
     <row r="239">
@@ -3421,7 +4249,7 @@
         <v>238</v>
       </c>
       <c r="B239" t="s">
-        <v>480</v>
+        <v>618</v>
       </c>
     </row>
     <row r="240">
@@ -3429,7 +4257,7 @@
         <v>239</v>
       </c>
       <c r="B240" t="s">
-        <v>481</v>
+        <v>619</v>
       </c>
     </row>
     <row r="241">
@@ -3437,7 +4265,7 @@
         <v>240</v>
       </c>
       <c r="B241" t="s">
-        <v>482</v>
+        <v>620</v>
       </c>
     </row>
     <row r="242">
@@ -3445,7 +4273,7 @@
         <v>241</v>
       </c>
       <c r="B242" t="s">
-        <v>483</v>
+        <v>621</v>
       </c>
     </row>
     <row r="243">
@@ -3453,7 +4281,1111 @@
         <v>242</v>
       </c>
       <c r="B243" t="s">
-        <v>484</v>
+        <v>622</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="s">
+        <v>243</v>
+      </c>
+      <c r="B244" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="s">
+        <v>244</v>
+      </c>
+      <c r="B245" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="s">
+        <v>245</v>
+      </c>
+      <c r="B246" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="s">
+        <v>246</v>
+      </c>
+      <c r="B247" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="s">
+        <v>247</v>
+      </c>
+      <c r="B248" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="s">
+        <v>248</v>
+      </c>
+      <c r="B249" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="s">
+        <v>249</v>
+      </c>
+      <c r="B250" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="s">
+        <v>250</v>
+      </c>
+      <c r="B251" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="s">
+        <v>251</v>
+      </c>
+      <c r="B252" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="s">
+        <v>252</v>
+      </c>
+      <c r="B253" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="s">
+        <v>253</v>
+      </c>
+      <c r="B254" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="s">
+        <v>254</v>
+      </c>
+      <c r="B255" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="s">
+        <v>255</v>
+      </c>
+      <c r="B256" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="s">
+        <v>256</v>
+      </c>
+      <c r="B257" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="s">
+        <v>257</v>
+      </c>
+      <c r="B258" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="s">
+        <v>258</v>
+      </c>
+      <c r="B259" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="s">
+        <v>259</v>
+      </c>
+      <c r="B260" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="s">
+        <v>260</v>
+      </c>
+      <c r="B261" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="s">
+        <v>261</v>
+      </c>
+      <c r="B262" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="s">
+        <v>262</v>
+      </c>
+      <c r="B263" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="s">
+        <v>263</v>
+      </c>
+      <c r="B264" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="s">
+        <v>264</v>
+      </c>
+      <c r="B265" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="s">
+        <v>265</v>
+      </c>
+      <c r="B266" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="s">
+        <v>266</v>
+      </c>
+      <c r="B267" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="s">
+        <v>267</v>
+      </c>
+      <c r="B268" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="s">
+        <v>268</v>
+      </c>
+      <c r="B269" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="s">
+        <v>269</v>
+      </c>
+      <c r="B270" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="s">
+        <v>270</v>
+      </c>
+      <c r="B271" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="s">
+        <v>271</v>
+      </c>
+      <c r="B272" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="s">
+        <v>272</v>
+      </c>
+      <c r="B273" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="s">
+        <v>273</v>
+      </c>
+      <c r="B274" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="s">
+        <v>274</v>
+      </c>
+      <c r="B275" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="s">
+        <v>275</v>
+      </c>
+      <c r="B276" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="s">
+        <v>276</v>
+      </c>
+      <c r="B277" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="s">
+        <v>277</v>
+      </c>
+      <c r="B278" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="s">
+        <v>278</v>
+      </c>
+      <c r="B279" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="s">
+        <v>279</v>
+      </c>
+      <c r="B280" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="s">
+        <v>280</v>
+      </c>
+      <c r="B281" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="s">
+        <v>281</v>
+      </c>
+      <c r="B282" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="s">
+        <v>282</v>
+      </c>
+      <c r="B283" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="s">
+        <v>283</v>
+      </c>
+      <c r="B284" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="s">
+        <v>284</v>
+      </c>
+      <c r="B285" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="s">
+        <v>285</v>
+      </c>
+      <c r="B286" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="s">
+        <v>286</v>
+      </c>
+      <c r="B287" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="s">
+        <v>287</v>
+      </c>
+      <c r="B288" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="s">
+        <v>288</v>
+      </c>
+      <c r="B289" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="s">
+        <v>289</v>
+      </c>
+      <c r="B290" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="s">
+        <v>290</v>
+      </c>
+      <c r="B291" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="s">
+        <v>291</v>
+      </c>
+      <c r="B292" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="s">
+        <v>292</v>
+      </c>
+      <c r="B293" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="s">
+        <v>293</v>
+      </c>
+      <c r="B294" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="s">
+        <v>294</v>
+      </c>
+      <c r="B295" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="s">
+        <v>295</v>
+      </c>
+      <c r="B296" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="s">
+        <v>296</v>
+      </c>
+      <c r="B297" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="s">
+        <v>297</v>
+      </c>
+      <c r="B298" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="s">
+        <v>298</v>
+      </c>
+      <c r="B299" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="s">
+        <v>299</v>
+      </c>
+      <c r="B300" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="s">
+        <v>300</v>
+      </c>
+      <c r="B301" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="s">
+        <v>301</v>
+      </c>
+      <c r="B302" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="s">
+        <v>302</v>
+      </c>
+      <c r="B303" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="s">
+        <v>303</v>
+      </c>
+      <c r="B304" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="s">
+        <v>304</v>
+      </c>
+      <c r="B305" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="s">
+        <v>305</v>
+      </c>
+      <c r="B306" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="s">
+        <v>306</v>
+      </c>
+      <c r="B307" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="s">
+        <v>307</v>
+      </c>
+      <c r="B308" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="s">
+        <v>308</v>
+      </c>
+      <c r="B309" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="s">
+        <v>309</v>
+      </c>
+      <c r="B310" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="s">
+        <v>310</v>
+      </c>
+      <c r="B311" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="s">
+        <v>311</v>
+      </c>
+      <c r="B312" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="s">
+        <v>312</v>
+      </c>
+      <c r="B313" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="s">
+        <v>313</v>
+      </c>
+      <c r="B314" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="s">
+        <v>314</v>
+      </c>
+      <c r="B315" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="s">
+        <v>315</v>
+      </c>
+      <c r="B316" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="s">
+        <v>316</v>
+      </c>
+      <c r="B317" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="s">
+        <v>317</v>
+      </c>
+      <c r="B318" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="s">
+        <v>318</v>
+      </c>
+      <c r="B319" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="s">
+        <v>319</v>
+      </c>
+      <c r="B320" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="s">
+        <v>320</v>
+      </c>
+      <c r="B321" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="s">
+        <v>321</v>
+      </c>
+      <c r="B322" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="s">
+        <v>322</v>
+      </c>
+      <c r="B323" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="s">
+        <v>323</v>
+      </c>
+      <c r="B324" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="s">
+        <v>324</v>
+      </c>
+      <c r="B325" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="s">
+        <v>325</v>
+      </c>
+      <c r="B326" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="s">
+        <v>326</v>
+      </c>
+      <c r="B327" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="s">
+        <v>327</v>
+      </c>
+      <c r="B328" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="s">
+        <v>328</v>
+      </c>
+      <c r="B329" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="s">
+        <v>329</v>
+      </c>
+      <c r="B330" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="s">
+        <v>330</v>
+      </c>
+      <c r="B331" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="s">
+        <v>331</v>
+      </c>
+      <c r="B332" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="s">
+        <v>332</v>
+      </c>
+      <c r="B333" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="s">
+        <v>333</v>
+      </c>
+      <c r="B334" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="s">
+        <v>334</v>
+      </c>
+      <c r="B335" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="s">
+        <v>335</v>
+      </c>
+      <c r="B336" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="s">
+        <v>336</v>
+      </c>
+      <c r="B337" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="s">
+        <v>337</v>
+      </c>
+      <c r="B338" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="s">
+        <v>338</v>
+      </c>
+      <c r="B339" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="s">
+        <v>339</v>
+      </c>
+      <c r="B340" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="s">
+        <v>340</v>
+      </c>
+      <c r="B341" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="s">
+        <v>341</v>
+      </c>
+      <c r="B342" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="s">
+        <v>342</v>
+      </c>
+      <c r="B343" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="s">
+        <v>343</v>
+      </c>
+      <c r="B344" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="s">
+        <v>344</v>
+      </c>
+      <c r="B345" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="s">
+        <v>345</v>
+      </c>
+      <c r="B346" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="s">
+        <v>346</v>
+      </c>
+      <c r="B347" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="s">
+        <v>347</v>
+      </c>
+      <c r="B348" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="s">
+        <v>348</v>
+      </c>
+      <c r="B349" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="s">
+        <v>349</v>
+      </c>
+      <c r="B350" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="s">
+        <v>350</v>
+      </c>
+      <c r="B351" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="s">
+        <v>351</v>
+      </c>
+      <c r="B352" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="s">
+        <v>352</v>
+      </c>
+      <c r="B353" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="s">
+        <v>353</v>
+      </c>
+      <c r="B354" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="s">
+        <v>354</v>
+      </c>
+      <c r="B355" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="s">
+        <v>355</v>
+      </c>
+      <c r="B356" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="s">
+        <v>356</v>
+      </c>
+      <c r="B357" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="s">
+        <v>357</v>
+      </c>
+      <c r="B358" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="s">
+        <v>358</v>
+      </c>
+      <c r="B359" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="s">
+        <v>359</v>
+      </c>
+      <c r="B360" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="s">
+        <v>360</v>
+      </c>
+      <c r="B361" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="s">
+        <v>361</v>
+      </c>
+      <c r="B362" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="s">
+        <v>362</v>
+      </c>
+      <c r="B363" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="s">
+        <v>363</v>
+      </c>
+      <c r="B364" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="s">
+        <v>364</v>
+      </c>
+      <c r="B365" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="s">
+        <v>365</v>
+      </c>
+      <c r="B366" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="s">
+        <v>366</v>
+      </c>
+      <c r="B367" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="s">
+        <v>367</v>
+      </c>
+      <c r="B368" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="s">
+        <v>368</v>
+      </c>
+      <c r="B369" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="s">
+        <v>369</v>
+      </c>
+      <c r="B370" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="s">
+        <v>370</v>
+      </c>
+      <c r="B371" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="s">
+        <v>371</v>
+      </c>
+      <c r="B372" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="s">
+        <v>372</v>
+      </c>
+      <c r="B373" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="s">
+        <v>373</v>
+      </c>
+      <c r="B374" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="s">
+        <v>374</v>
+      </c>
+      <c r="B375" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="s">
+        <v>375</v>
+      </c>
+      <c r="B376" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="s">
+        <v>376</v>
+      </c>
+      <c r="B377" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="s">
+        <v>377</v>
+      </c>
+      <c r="B378" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="s">
+        <v>378</v>
+      </c>
+      <c r="B379" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="s">
+        <v>379</v>
+      </c>
+      <c r="B380" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="s">
+        <v>380</v>
+      </c>
+      <c r="B381" t="s">
+        <v>760</v>
       </c>
     </row>
   </sheetData>
